--- a/prisma/VERIFICATION_LOG_GENERADO.xlsx
+++ b/prisma/VERIFICATION_LOG_GENERADO.xlsx
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -1533,42 +1533,42 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>articulo_000555</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="4" t="n">
         <v>2024</v>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>GPT Assisted Annotation of Rhetorical and Linguistic Features for Interpretable Propaganda Technique Detection</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>✓ Exacto</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="E25" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>~ Adyacente</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="26">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>9</v>
@@ -1869,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>4</v>
@@ -1888,7 +1888,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -1973,7 +1973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>13/30 = 43.3%</t>
+          <t>12/30 = 40.0%</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>16/30 = 53.3%</t>
+          <t>17/30 = 56.7%</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -2059,15 +2059,32 @@
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
         <is>
+          <t>Acuerdo exacto + adyacente (≤ 1 nivel)</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>29/30 = 96.7%</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Cifra reportada en el paper como discrepancias adyacentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
           <t>Desacuerdo extremo</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>1/30 = 3.3%</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Diferencia de 2 niveles (A↔B)</t>
         </is>
@@ -2081,7 +2098,7 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
@@ -2098,146 +2115,163 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Fair agreement</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Distribución LLM - Alta (A)</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>17/30</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>56.7%</t>
+          <t>Slight agreement (Landis &amp; Koch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Cohen's Kappa ponderado lineal (κw)</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>0.174</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Slight agreement (Landis &amp; Koch)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>Distribución LLM - Media (M)</t>
+          <t>Distribución LLM - Alta (A)</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>16/30</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
+          <t>Distribución LLM - Media (M)</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
           <t>Distribución LLM - Baja (B)</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>4/30</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>13.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>Distribución Humano - Alta (A)</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>10/30</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>Distribución Humano - Media (M)</t>
+          <t>Distribución Humano - Alta (A)</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>10/30</t>
         </is>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
         <is>
+          <t>Distribución Humano - Media (M)</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
           <t>Distribución Humano - Baja (B)</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>5/30</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>16.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>Sesgo sistemático detectado</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>LLM sobreclasifica en categoría Alta</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>LLM asignó A a 17 artículos vs 10 del evaluador humano</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
+          <t>Sesgo sistemático detectado</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>LLM sobreclasifica en categoría Alta</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>LLM asignó A a 16 artículos vs 10 del evaluador humano</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
           <t>Umbral de inclusión pipeline</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>≥ 0.4 (categorías A y M)</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>El umbral captura artículos de relevancia media y alta</t>
         </is>
@@ -2257,7 +2291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2418,7 +2452,7 @@
         </is>
       </c>
       <c r="E4" s="28" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
@@ -2894,23 +2928,23 @@
     </row>
     <row r="16">
       <c r="A16" s="28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" s="28" t="inlineStr">
         <is>
-          <t>articulo_003289</t>
+          <t>articulo_000555</t>
         </is>
       </c>
       <c r="C16" s="28" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D16" s="29" t="inlineStr">
         <is>
-          <t>XAI in Automated Fact-Checking? The Benefits Are Modest and There's No One-Explanation-Fits-All</t>
+          <t>GPT Assisted Annotation of Rhetorical and Linguistic Features for Interpretable Propaganda Technique Detection</t>
         </is>
       </c>
       <c r="E16" s="28" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="F16" s="28" t="inlineStr">
         <is>
@@ -2919,97 +2953,138 @@
       </c>
       <c r="G16" s="28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" s="28" t="inlineStr">
         <is>
-          <t>M→B</t>
+          <t>M→A</t>
         </is>
       </c>
       <c r="I16" s="29" t="inlineStr">
         <is>
-          <t>LLM asignó relevancia media; evaluador considera fuera del scope del tema</t>
+          <t>Subclasificación LLM: artículo con intenciones explícitas que el evaluador reconoció como alta relevancia</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="28" t="inlineStr">
         <is>
-          <t>articulo_001001</t>
+          <t>articulo_003289</t>
         </is>
       </c>
       <c r="C17" s="28" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>A Perturbation-Theoretic Model for Fact-Checker Deployment in Dynamic Disinformation Networks</t>
+          <t>XAI in Automated Fact-Checking? The Benefits Are Modest and There's No One-Explanation-Fits-All</t>
         </is>
       </c>
       <c r="E17" s="28" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="H17" s="28" t="inlineStr">
         <is>
-          <t>B→M</t>
+          <t>M→B</t>
         </is>
       </c>
       <c r="I17" s="29" t="inlineStr">
         <is>
-          <t>LLM infra-detectó relevancia; artículo tiene componente de intención relevante según evaluador</t>
+          <t>LLM asignó relevancia media; evaluador considera fuera del scope del tema</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>articulo_001001</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>A Perturbation-Theoretic Model for Fact-Checker Deployment in Dynamic Disinformation Networks</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>B→M</t>
+        </is>
+      </c>
+      <c r="I18" s="29" t="inlineStr">
+        <is>
+          <t>LLM infra-detectó relevancia; artículo tiene componente de intención relevante según evaluador</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="n">
         <v>28</v>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>articulo_001003</t>
         </is>
       </c>
-      <c r="C18" s="28" t="n">
+      <c r="C19" s="28" t="n">
         <v>2022</v>
       </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>The fake news effect: what does it mean for consumer behavioral intentions towards brands?</t>
         </is>
       </c>
-      <c r="E18" s="28" t="n">
+      <c r="E19" s="28" t="n">
         <v>0.35</v>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H18" s="28" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
         <is>
           <t>B→M</t>
         </is>
       </c>
-      <c r="I18" s="29" t="inlineStr">
+      <c r="I19" s="29" t="inlineStr">
         <is>
           <t>LLM infra-detectó relevancia; artículo tiene componente de intención relevante según evaluador</t>
         </is>
